--- a/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,61 +656,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -718,28 +724,34 @@
         <v>4</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
+      <c r="J8" s="3">
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -747,16 +759,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>4</v>
@@ -767,8 +779,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -776,16 +794,16 @@
         <v>4</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
+      <c r="H10" s="3">
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>4</v>
@@ -796,8 +814,14 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,37 +833,45 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E12" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F12" s="3">
         <v>9400</v>
       </c>
-      <c r="E12" s="3">
-        <v>18500</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H12" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I12" s="3">
         <v>8600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="J12" s="3">
         <v>8500</v>
       </c>
-      <c r="H12" s="3">
-        <v>17200</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>7800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>6400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,13 +899,19 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -884,20 +922,26 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>300</v>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +969,14 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,37 +985,45 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F17" s="3">
         <v>13900</v>
       </c>
-      <c r="E17" s="3">
-        <v>24100</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>11900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>12100</v>
+      </c>
+      <c r="I17" s="3">
         <v>11400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
         <v>11600</v>
       </c>
-      <c r="H17" s="3">
-        <v>26700</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>12000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -973,28 +1031,34 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
+        <v>-13000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-13900</v>
       </c>
       <c r="G18" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
         <v>-11600</v>
       </c>
-      <c r="H18" s="3">
-        <v>-26700</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,8 +1070,10 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1015,28 +1081,34 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>-18200</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+        <v>-6200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-1800</v>
       </c>
       <c r="G20" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="H20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1044,28 +1116,34 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>-42000</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
+        <v>-19100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-15700</v>
       </c>
       <c r="G21" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="3">
         <v>-11000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-24200</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,37 +1171,49 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-15700</v>
       </c>
-      <c r="E23" s="3">
-        <v>-42200</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-10900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>-11100</v>
       </c>
-      <c r="H23" s="3">
-        <v>-24500</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-12500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-9100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1151,8 +1241,14 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1276,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-15700</v>
       </c>
-      <c r="E26" s="3">
-        <v>-42200</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-10900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>-11100</v>
       </c>
-      <c r="H26" s="3">
-        <v>-24500</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-12500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-9100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-20100</v>
       </c>
-      <c r="E27" s="3">
-        <v>-50700</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-15200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="J27" s="3">
         <v>-15400</v>
       </c>
-      <c r="H27" s="3">
-        <v>-33100</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-16900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-13400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1381,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1416,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1451,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,8 +1486,14 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1363,57 +1501,69 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>18200</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+        <v>6200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1800</v>
       </c>
       <c r="G32" s="3">
+        <v>18400</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-20100</v>
       </c>
-      <c r="E33" s="3">
-        <v>-50700</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="I33" s="3">
         <v>-15200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="J33" s="3">
         <v>-15400</v>
       </c>
-      <c r="H33" s="3">
-        <v>-33100</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-16900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-13400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1591,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-20100</v>
       </c>
-      <c r="E35" s="3">
-        <v>-50700</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="I35" s="3">
         <v>-15200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="J35" s="3">
         <v>-15400</v>
       </c>
-      <c r="H35" s="3">
-        <v>-33100</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-16900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-13400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1685,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,23 +1700,25 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>121400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>33200</v>
+      </c>
+      <c r="F41" s="3">
         <v>44500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>27700</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1559,8 +1731,14 @@
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,8 +1766,14 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1597,14 +1781,14 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1617,8 +1801,14 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1628,11 +1818,11 @@
       <c r="E44" s="3">
         <v>100</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
+      <c r="F44" s="3">
+        <v>100</v>
+      </c>
+      <c r="G44" s="3">
+        <v>100</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
@@ -1646,23 +1836,29 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F45" s="3">
         <v>2200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
@@ -1675,23 +1871,29 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>35600</v>
+      </c>
+      <c r="F46" s="3">
         <v>46800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>29400</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H46" s="3" t="s">
         <v>4</v>
       </c>
@@ -1704,8 +1906,14 @@
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1733,23 +1941,29 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>30800</v>
+      </c>
+      <c r="F48" s="3">
         <v>900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>4</v>
       </c>
@@ -1762,8 +1976,14 @@
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1791,8 +2011,14 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2046,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,23 +2081,29 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F52" s="3">
         <v>9000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>8100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>4</v>
       </c>
@@ -1878,8 +2116,14 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,23 +2151,29 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>163500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>76200</v>
+      </c>
+      <c r="F54" s="3">
         <v>56800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>38600</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>4</v>
       </c>
@@ -1936,8 +2186,14 @@
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2205,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,23 +2220,25 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>4</v>
       </c>
@@ -1991,8 +2251,14 @@
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2020,23 +2286,29 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F59" s="3">
         <v>7700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6900</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2049,23 +2321,29 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F60" s="3">
         <v>8400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7400</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2078,23 +2356,29 @@
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>55200</v>
+      </c>
+      <c r="F61" s="3">
         <v>54700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>36400</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2107,22 +2391,28 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>47600</v>
+      </c>
+      <c r="F62" s="3">
         <v>13500</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
+      <c r="G62" s="3">
+        <v>0</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>4</v>
@@ -2136,8 +2426,14 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2461,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2496,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,23 +2531,29 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>113900</v>
+      </c>
+      <c r="F66" s="3">
         <v>76600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>43800</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2252,8 +2566,14 @@
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2585,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2616,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,22 +2651,28 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>287300</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>287300</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>287300</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>287300</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2352,8 +2686,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,23 +2721,29 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-349900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-346600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-327400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-311700</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>4</v>
       </c>
@@ -2410,8 +2756,14 @@
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2791,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2826,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,23 +2861,29 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>84200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-325100</v>
+      </c>
+      <c r="F76" s="3">
         <v>-307200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-292500</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>4</v>
       </c>
@@ -2526,8 +2896,14 @@
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2931,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-20100</v>
       </c>
-      <c r="E81" s="3">
-        <v>-50700</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="I81" s="3">
         <v>-15200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="J81" s="3">
         <v>-15400</v>
       </c>
-      <c r="H81" s="3">
-        <v>-33100</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-16900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-13400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,8 +3025,10 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2640,7 +3036,7 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -2649,19 +3045,25 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
       </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3091,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3126,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3161,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3196,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3231,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-11000</v>
       </c>
-      <c r="E89" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-12500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>-9700</v>
       </c>
-      <c r="H89" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-9900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-9300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,19 +3285,21 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-1100</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -2871,13 +3311,19 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3351,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,19 +3386,25 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>-1100</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G94" s="3">
         <v>-100</v>
@@ -2958,13 +3416,19 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3440,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3471,14 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3506,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3541,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3576,49 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F100" s="3">
         <v>28000</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>13400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>86500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,33 +3646,45 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>88200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="F102" s="3">
         <v>16800</v>
       </c>
-      <c r="E102" s="3">
-        <v>-21300</v>
-      </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="I102" s="3">
         <v>-12500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-9700</v>
       </c>
-      <c r="H102" s="3">
-        <v>-19700</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-9900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>4100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>72200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>GUTS</t>
   </si>
@@ -656,67 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -730,19 +734,19 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>4</v>
@@ -750,8 +754,11 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -770,8 +777,8 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
+      <c r="I9" s="3">
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>4</v>
@@ -785,8 +792,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -800,13 +810,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
+      <c r="I10" s="3">
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>4</v>
@@ -820,8 +830,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,43 +848,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E12" s="3">
         <v>14400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,16 +922,19 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -922,11 +942,11 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -934,14 +954,17 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -975,8 +998,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,43 +1013,47 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E17" s="3">
         <v>21600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1031,34 +1061,37 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-13000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12100</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>-11600</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,8 +1105,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1081,34 +1115,37 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-6200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-18400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1116,34 +1153,37 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-19100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-30100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11900</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3">
         <v>-11000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1177,43 +1217,49 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-30200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1247,8 +1293,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,78 +1331,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-30200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1445,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1483,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1521,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,8 +1559,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1501,69 +1571,75 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="F32" s="3">
         <v>6200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>18400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,83 +1673,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1772,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,26 +1788,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>102400</v>
+      </c>
+      <c r="E41" s="3">
         <v>121400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>44500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>27700</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1737,8 +1824,11 @@
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1772,8 +1862,11 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1787,11 +1880,11 @@
         <v>0</v>
       </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1807,8 +1900,11 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1824,8 +1920,8 @@
       <c r="G44" s="3">
         <v>100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
+      <c r="H44" s="3">
+        <v>100</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>4</v>
@@ -1842,26 +1938,29 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1600</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
@@ -1877,26 +1976,29 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>106600</v>
+      </c>
+      <c r="E46" s="3">
         <v>124500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>46800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29400</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>4</v>
       </c>
@@ -1912,8 +2014,11 @@
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1947,26 +2052,29 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E48" s="3">
         <v>31500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>4</v>
       </c>
@@ -1982,8 +2090,11 @@
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2017,8 +2128,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2166,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,26 +2204,29 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E52" s="3">
         <v>7500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2122,8 +2242,11 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,26 +2280,29 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>146400</v>
+      </c>
+      <c r="E54" s="3">
         <v>163500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>76200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>56800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38600</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2192,8 +2318,11 @@
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2336,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,26 +2352,27 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2257,8 +2388,11 @@
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2292,26 +2426,29 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E59" s="3">
         <v>12200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6900</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2327,26 +2464,29 @@
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E60" s="3">
         <v>13300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7400</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2362,26 +2502,29 @@
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E61" s="3">
         <v>28700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>55200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>54700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36400</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2397,25 +2540,28 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E62" s="3">
         <v>37400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>47600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13500</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -2432,8 +2578,11 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2616,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2654,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,26 +2692,29 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>75700</v>
+      </c>
+      <c r="E66" s="3">
         <v>79300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>113900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>76600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43800</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2572,8 +2730,11 @@
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2748,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2784,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2822,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2666,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>287300</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
         <v>287300</v>
@@ -2675,7 +2843,7 @@
         <v>287300</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>287300</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -2692,8 +2860,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,26 +2898,29 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-367200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-349900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-346600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-327400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-311700</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
@@ -2762,8 +2936,11 @@
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +2974,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3012,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,26 +3050,29 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E76" s="3">
         <v>84200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-325100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-307200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-292500</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>4</v>
       </c>
@@ -2902,8 +3088,11 @@
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,83 +3126,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,19 +3225,20 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -3057,13 +3256,16 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3299,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3337,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3375,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3413,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3451,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,16 +3507,17 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
@@ -3305,25 +3526,28 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3581,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,16 +3619,19 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1100</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-100</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
@@ -3410,25 +3640,28 @@
         <v>-100</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,8 +3675,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3477,8 +3711,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3749,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +3787,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,23 +3825,26 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>101000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>28000</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -3612,13 +3858,16 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>13400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>86500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3652,39 +3901,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E102" s="3">
         <v>88200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>72200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
   <si>
     <t>GUTS</t>
   </si>
@@ -656,71 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -737,19 +741,19 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>4</v>
@@ -757,8 +761,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -780,8 +787,8 @@
       <c r="I9" s="3">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -795,13 +802,16 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>0</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -813,13 +823,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
+      <c r="J10" s="3">
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
@@ -833,8 +843,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,46 +862,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E12" s="3">
         <v>16800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,31 +942,34 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>300</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-6700</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+        <v>1100</v>
+      </c>
+      <c r="I14" s="3">
+        <v>18400</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -957,37 +977,40 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1001,8 +1024,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,84 +1040,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E17" s="3">
         <v>23000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-23800</v>
       </c>
       <c r="E18" s="3">
-        <v>-21600</v>
+        <v>-23000</v>
       </c>
       <c r="F18" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="G18" s="3">
         <v>-13000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13900</v>
       </c>
-      <c r="H18" s="3">
-        <v>-11800</v>
-      </c>
       <c r="I18" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-12100</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3">
         <v>-11600</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,107 +1139,114 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-2300</v>
       </c>
       <c r="E20" s="3">
-        <v>18300</v>
+        <v>-4700</v>
       </c>
       <c r="F20" s="3">
-        <v>-6200</v>
+        <v>-10400</v>
       </c>
       <c r="G20" s="3">
-        <v>-1800</v>
+        <v>5600</v>
       </c>
       <c r="H20" s="3">
-        <v>-18400</v>
+        <v>1000</v>
       </c>
       <c r="I20" s="3">
-        <v>200</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-21300</v>
       </c>
       <c r="E21" s="3">
-        <v>-3300</v>
+        <v>-18100</v>
       </c>
       <c r="F21" s="3">
-        <v>-19100</v>
+        <v>-11100</v>
       </c>
       <c r="G21" s="3">
-        <v>-15700</v>
+        <v>-18600</v>
       </c>
       <c r="H21" s="3">
-        <v>-30100</v>
+        <v>-14800</v>
       </c>
       <c r="I21" s="3">
         <v>-11900</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="J21" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3">
         <v>-11000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1220,69 +1260,75 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1296,8 +1342,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,84 +1383,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1547,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,84 +1629,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>2300</v>
       </c>
       <c r="E32" s="3">
-        <v>-18300</v>
+        <v>4700</v>
       </c>
       <c r="F32" s="3">
-        <v>6200</v>
+        <v>10400</v>
       </c>
       <c r="G32" s="3">
-        <v>1800</v>
+        <v>-5600</v>
       </c>
       <c r="H32" s="3">
-        <v>18400</v>
+        <v>-1000</v>
       </c>
       <c r="I32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17200</v>
       </c>
-      <c r="E33" s="3">
-        <v>-5100</v>
-      </c>
       <c r="F33" s="3">
-        <v>-23500</v>
+        <v>-3300</v>
       </c>
       <c r="G33" s="3">
-        <v>-20100</v>
+        <v>-19200</v>
       </c>
       <c r="H33" s="3">
-        <v>-34500</v>
+        <v>-15700</v>
       </c>
       <c r="I33" s="3">
-        <v>-16200</v>
+        <v>-30200</v>
       </c>
       <c r="J33" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-15200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,89 +1752,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17200</v>
       </c>
-      <c r="E35" s="3">
-        <v>-5100</v>
-      </c>
       <c r="F35" s="3">
-        <v>-23500</v>
+        <v>-3300</v>
       </c>
       <c r="G35" s="3">
-        <v>-20100</v>
+        <v>-19200</v>
       </c>
       <c r="H35" s="3">
-        <v>-34500</v>
+        <v>-15700</v>
       </c>
       <c r="I35" s="3">
-        <v>-16200</v>
+        <v>-30200</v>
       </c>
       <c r="J35" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-15200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,29 +1875,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E41" s="3">
         <v>102400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>121400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>44500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>27700</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1827,8 +1914,11 @@
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1865,13 +1955,16 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -1883,11 +1976,11 @@
         <v>0</v>
       </c>
       <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1903,8 +1996,11 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1923,8 +2019,8 @@
       <c r="H44" s="3">
         <v>100</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
+      <c r="I44" s="3">
+        <v>100</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
@@ -1941,25 +2037,28 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>4000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1600</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
@@ -1979,29 +2078,32 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>87700</v>
+      </c>
+      <c r="E46" s="3">
         <v>106600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>124500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>46800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29400</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2017,31 +2119,34 @@
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2055,29 +2160,32 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E48" s="3">
         <v>32300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2093,8 +2201,11 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2131,8 +2242,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,28 +2324,31 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E52" s="3">
         <v>7600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7500</v>
       </c>
-      <c r="F52" s="3">
-        <v>9800</v>
-      </c>
       <c r="G52" s="3">
-        <v>9000</v>
+        <v>6800</v>
       </c>
       <c r="H52" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
+        <v>6800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>7100</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
@@ -2245,8 +2365,11 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,29 +2406,32 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>126900</v>
+      </c>
+      <c r="E54" s="3">
         <v>146400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>163500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>76200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>56800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38600</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2321,8 +2447,11 @@
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,29 +2483,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2391,28 +2522,31 @@
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2429,28 +2563,31 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12000</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>12200</v>
+        <v>400</v>
       </c>
       <c r="F59" s="3">
-        <v>10600</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
-        <v>7700</v>
+        <v>600</v>
       </c>
       <c r="H59" s="3">
-        <v>6900</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
+        <v>600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>500</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
@@ -2467,29 +2604,32 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E60" s="3">
         <v>14300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7400</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2505,29 +2645,32 @@
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28400</v>
+        <v>58000</v>
       </c>
       <c r="E61" s="3">
-        <v>28700</v>
+        <v>56300</v>
       </c>
       <c r="F61" s="3">
-        <v>55200</v>
+        <v>56900</v>
       </c>
       <c r="G61" s="3">
+        <v>83700</v>
+      </c>
+      <c r="H61" s="3">
         <v>54700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36400</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2543,25 +2686,28 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>33000</v>
+        <v>2900</v>
       </c>
       <c r="E62" s="3">
-        <v>37400</v>
+        <v>5100</v>
       </c>
       <c r="F62" s="3">
-        <v>47600</v>
+        <v>9100</v>
       </c>
       <c r="G62" s="3">
-        <v>13500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
+        <v>19100</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -2581,8 +2727,11 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,29 +2850,32 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E66" s="3">
         <v>75700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>79300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>113900</v>
       </c>
-      <c r="G66" s="3">
-        <v>76600</v>
-      </c>
       <c r="H66" s="3">
+        <v>63100</v>
+      </c>
+      <c r="I66" s="3">
         <v>43800</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2733,8 +2891,11 @@
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2837,19 +3005,19 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>287300</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
         <v>287300</v>
       </c>
       <c r="H70" s="3">
+        <v>300800</v>
+      </c>
+      <c r="I70" s="3">
         <v>287300</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>287300</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -2863,8 +3031,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,29 +3072,32 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-390300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-367200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-349900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-346600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-327400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-311700</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
@@ -2939,8 +3113,11 @@
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,31 +3236,34 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E76" s="3">
         <v>70800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>84200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-325100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-307200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-292500</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
+      <c r="J76" s="3">
+        <v>-252300</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
@@ -3091,8 +3277,11 @@
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,89 +3318,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17200</v>
       </c>
-      <c r="E81" s="3">
-        <v>-5100</v>
-      </c>
       <c r="F81" s="3">
-        <v>-23500</v>
+        <v>-3300</v>
       </c>
       <c r="G81" s="3">
-        <v>-20100</v>
+        <v>-19200</v>
       </c>
       <c r="H81" s="3">
-        <v>-34500</v>
+        <v>-15700</v>
       </c>
       <c r="I81" s="3">
-        <v>-16200</v>
+        <v>-30200</v>
       </c>
       <c r="J81" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-15200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,19 +3424,20 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
-      </c>
-      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -3259,13 +3458,16 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
+        <v>100</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,46 +3668,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11000</v>
       </c>
-      <c r="H89" s="3">
-        <v>-11700</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
         <v>-12500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,19 +3728,20 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -3528,26 +3749,29 @@
       <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,19 +3849,22 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1100</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-100</v>
       </c>
       <c r="G94" s="3">
         <v>-100</v>
@@ -3642,26 +3872,29 @@
       <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,31 +3909,32 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3714,8 +3948,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,31 +4071,34 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>101000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>28000</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -3861,36 +4107,39 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>13400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>86500</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3904,42 +4153,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>88200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16800</v>
       </c>
-      <c r="H102" s="3">
-        <v>-11700</v>
-      </c>
       <c r="I102" s="3">
-        <v>-9600</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-12500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>72200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>GUTS</t>
   </si>
@@ -656,75 +656,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -744,19 +747,19 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>4</v>
@@ -764,8 +767,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -790,8 +796,8 @@
       <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
+      <c r="K9" s="3">
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
@@ -805,8 +811,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -831,8 +840,8 @@
       <c r="J10" s="3">
         <v>0</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
+      <c r="K10" s="3">
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
@@ -846,8 +855,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,49 +875,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E12" s="3">
         <v>19000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,49 +961,55 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>900</v>
+      </c>
+      <c r="E14" s="3">
         <v>2600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-6700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>18400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -998,13 +1020,13 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
+        <v>200</v>
+      </c>
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
@@ -1013,7 +1035,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1027,8 +1049,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,90 +1066,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E17" s="3">
         <v>23800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-23800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-23000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-11600</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,90 +1172,97 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-10400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-14800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>-11000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1248,8 +1287,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1263,49 +1302,55 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-30200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1330,8 +1375,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1345,8 +1390,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,90 +1434,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1566,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1610,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1654,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,90 +1698,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,95 +1830,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1943,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,32 +1961,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E41" s="3">
         <v>84700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>102400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>121400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>44500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27700</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1917,8 +2003,11 @@
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1958,16 +2047,19 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -1979,11 +2071,11 @@
         <v>0</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1999,8 +2091,11 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2022,8 +2117,8 @@
       <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
+      <c r="J44" s="3">
+        <v>100</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
@@ -2040,8 +2135,11 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2081,32 +2179,35 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E46" s="3">
         <v>87700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>106600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>124500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>46800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29400</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2122,8 +2223,11 @@
       <c r="O46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2148,8 +2252,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2163,32 +2267,35 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E48" s="3">
         <v>31800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2204,8 +2311,11 @@
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2245,8 +2355,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2399,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,32 +2443,35 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E52" s="3">
         <v>7500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>6800</v>
       </c>
       <c r="H52" s="3">
         <v>6800</v>
       </c>
       <c r="I52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J52" s="3">
         <v>7100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2368,8 +2487,11 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,32 +2531,35 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>108100</v>
+      </c>
+      <c r="E54" s="3">
         <v>126900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>146400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>163500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>76200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>56800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38600</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2450,8 +2575,11 @@
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2595,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,32 +2613,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2525,32 +2655,35 @@
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="E58" s="3">
         <v>4900</v>
       </c>
       <c r="F58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G58" s="3">
         <v>3600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -2566,32 +2699,35 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E59" s="3">
         <v>400</v>
       </c>
       <c r="F59" s="3">
+        <v>400</v>
+      </c>
+      <c r="G59" s="3">
         <v>100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>600</v>
       </c>
       <c r="H59" s="3">
         <v>600</v>
       </c>
       <c r="I59" s="3">
+        <v>600</v>
+      </c>
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2607,32 +2743,35 @@
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E60" s="3">
         <v>15700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2648,32 +2787,35 @@
       <c r="O60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E61" s="3">
         <v>58000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>56300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>56900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>83700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2689,26 +2831,29 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E62" s="3">
         <v>2900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>19100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
@@ -2730,8 +2875,11 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2919,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2963,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,32 +3007,35 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E66" s="3">
         <v>76600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>75700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>79300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>113900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43800</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2894,8 +3051,11 @@
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3071,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3113,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3157,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3008,19 +3175,19 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>287300</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>300800</v>
-      </c>
-      <c r="I70" s="3">
-        <v>287300</v>
       </c>
       <c r="J70" s="3">
         <v>287300</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>287300</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -3034,8 +3201,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,32 +3245,35 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-415300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-390300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-367200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-349900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-346600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-327400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-311700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3116,8 +3289,11 @@
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3333,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3377,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,35 +3421,38 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E76" s="3">
         <v>50300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>70800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>84200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-325100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-307200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-292500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-252300</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3280,8 +3465,11 @@
       <c r="O76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,95 +3509,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,22 +3622,23 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G83" s="3">
-        <v>100</v>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -3461,13 +3659,16 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3708,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3752,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3796,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3840,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +3884,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3">
         <v>-12500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,8 +3948,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3738,40 +3958,43 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
+      <c r="I91" s="3">
+        <v>-100</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4034,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,8 +4078,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3861,40 +4090,43 @@
         <v>-200</v>
       </c>
       <c r="E94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-100</v>
       </c>
       <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
+      <c r="I94" s="3">
+        <v>-100</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,8 +4142,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3936,8 +4169,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3951,8 +4184,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4228,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4272,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,34 +4316,37 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>101000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>28000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -4110,13 +4355,16 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>13400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>86500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4141,8 +4389,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4156,45 +4404,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>88200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16800</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-12500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>72200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>GUTS</t>
   </si>
@@ -656,78 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -750,19 +754,19 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>4</v>
@@ -770,13 +774,16 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -799,8 +806,8 @@
       <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
+      <c r="L9" s="3">
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
@@ -814,13 +821,16 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -843,8 +853,8 @@
       <c r="K10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
@@ -858,8 +868,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,52 +889,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E12" s="3">
         <v>20300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,57 +981,63 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-6700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>18400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1023,13 +1046,13 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
+        <v>200</v>
+      </c>
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -1038,7 +1061,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1052,8 +1075,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,96 +1093,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E17" s="3">
         <v>25200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-25200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-23800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-21500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>-11600</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,96 +1206,103 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-24500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-21300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-11900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>-11000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1290,8 +1330,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1305,52 +1345,58 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1378,8 +1424,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1393,8 +1439,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,96 +1486,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,96 +1768,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>800</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-30200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,101 +1909,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-30200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,35 +2048,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E41" s="3">
         <v>67500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>84700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>102400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>121400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>44500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>27700</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2006,8 +2093,11 @@
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2050,8 +2140,11 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2061,8 +2154,8 @@
       <c r="E43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -2074,11 +2167,11 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2094,13 +2187,16 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>100</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E44" s="3">
         <v>100</v>
@@ -2120,8 +2216,8 @@
       <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
+      <c r="K44" s="3">
+        <v>100</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
@@ -2138,8 +2234,11 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2182,35 +2281,38 @@
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E46" s="3">
         <v>71800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>87700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>106600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>124500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>46800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>29400</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2226,8 +2328,11 @@
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2255,8 +2360,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2270,35 +2375,38 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E48" s="3">
         <v>31400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2314,8 +2422,11 @@
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2358,8 +2469,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,35 +2563,38 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E52" s="3">
         <v>4300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7500</v>
-      </c>
-      <c r="H52" s="3">
-        <v>6800</v>
       </c>
       <c r="I52" s="3">
         <v>6800</v>
       </c>
       <c r="J52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K52" s="3">
         <v>7100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2490,8 +2610,11 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,35 +2657,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E54" s="3">
         <v>108100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>126900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>146400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>163500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>76200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>56800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2578,8 +2704,11 @@
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,35 +2744,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2658,8 +2789,11 @@
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2667,26 +2801,26 @@
         <v>5000</v>
       </c>
       <c r="E58" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="F58" s="3">
         <v>4900</v>
       </c>
       <c r="G58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H58" s="3">
         <v>3600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2702,35 +2836,38 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>800</v>
-      </c>
-      <c r="E59" s="3">
-        <v>400</v>
       </c>
       <c r="F59" s="3">
         <v>400</v>
       </c>
       <c r="G59" s="3">
+        <v>400</v>
+      </c>
+      <c r="H59" s="3">
         <v>100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>600</v>
       </c>
       <c r="I59" s="3">
         <v>600</v>
       </c>
       <c r="J59" s="3">
+        <v>600</v>
+      </c>
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2746,35 +2883,38 @@
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E60" s="3">
         <v>19800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7400</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2790,35 +2930,38 @@
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E61" s="3">
         <v>57500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>58000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>56300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>56900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>83700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>54700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>36400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2834,29 +2977,32 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
@@ -2878,8 +3024,11 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,35 +3165,38 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E66" s="3">
         <v>79700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>76600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>75700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>79300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>113900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>43800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3054,8 +3212,11 @@
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3178,19 +3346,19 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>287300</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>300800</v>
-      </c>
-      <c r="J70" s="3">
-        <v>287300</v>
       </c>
       <c r="K70" s="3">
         <v>287300</v>
       </c>
       <c r="L70" s="3">
-        <v>0</v>
+        <v>287300</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
@@ -3204,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,35 +3419,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-439000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-415300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-390300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-367200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-349900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-346600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-327400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-311700</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3292,8 +3466,11 @@
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,38 +3607,41 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E76" s="3">
         <v>28400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>50300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>70800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>84200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-325100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-307200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-292500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-252300</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3468,8 +3654,11 @@
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,101 +3701,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-30200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,25 +3821,26 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H83" s="3">
-        <v>100</v>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -3662,13 +3861,16 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,52 +4101,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>-12500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,52 +4169,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>4</v>
+      <c r="J91" s="3">
+        <v>-100</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,52 +4308,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="E94" s="3">
         <v>-200</v>
       </c>
       <c r="F94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-100</v>
       </c>
       <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
+      <c r="J94" s="3">
+        <v>-100</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4172,8 +4406,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4187,8 +4421,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,37 +4562,40 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>101000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>28000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -4358,13 +4604,16 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>13400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>86500</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4392,8 +4641,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4407,48 +4656,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>88200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16800</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-12500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>72200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>GUTS</t>
   </si>
@@ -656,90 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -757,19 +761,19 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>4</v>
@@ -777,16 +781,19 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -809,8 +816,8 @@
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
+      <c r="M9" s="3">
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
@@ -824,16 +831,19 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -856,8 +866,8 @@
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
@@ -871,8 +881,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,55 +903,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E12" s="3">
         <v>19400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>16800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,55 +1001,61 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-6700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>18400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1040,7 +1063,7 @@
         <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>200</v>
@@ -1049,13 +1072,13 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1064,7 +1087,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1078,8 +1101,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,102 +1120,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E17" s="3">
         <v>24800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-25200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-23000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-21500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>-11600</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,102 +1240,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-23700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-24500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-21300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>-11000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1333,8 +1373,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1348,55 +1388,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-30200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1427,8 +1473,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1442,8 +1488,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,102 +1538,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,102 +1838,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-30200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,107 +1988,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-30200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,38 +2135,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E41" s="3">
         <v>42100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>67500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>84700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>102400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>121400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>44500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>27700</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2096,8 +2183,11 @@
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,8 +2233,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2157,8 +2250,8 @@
       <c r="F43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
@@ -2170,11 +2263,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2190,16 +2283,19 @@
       <c r="Q43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
-        <v>100</v>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F44" s="3">
         <v>100</v>
@@ -2219,8 +2315,8 @@
       <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
+      <c r="L44" s="3">
+        <v>100</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
@@ -2237,8 +2333,11 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2284,38 +2383,41 @@
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E46" s="3">
         <v>47000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>71800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>87700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>106600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>124500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29400</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2331,8 +2433,11 @@
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2363,8 +2468,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2378,38 +2483,41 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E48" s="3">
         <v>31200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>30800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1100</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2425,8 +2533,11 @@
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2472,8 +2583,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,38 +2683,41 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E52" s="3">
         <v>4800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>6800</v>
       </c>
       <c r="J52" s="3">
         <v>6800</v>
       </c>
       <c r="K52" s="3">
+        <v>6800</v>
+      </c>
+      <c r="L52" s="3">
         <v>7100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2613,8 +2733,11 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,38 +2783,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E54" s="3">
         <v>83000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>108100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>126900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>146400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>163500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>76200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>56800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2707,8 +2833,11 @@
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,38 +2875,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2792,8 +2923,11 @@
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2804,26 +2938,26 @@
         <v>5000</v>
       </c>
       <c r="F58" s="3">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G58" s="3">
         <v>4900</v>
       </c>
       <c r="H58" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I58" s="3">
         <v>3600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2839,8 +2973,11 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2848,29 +2985,29 @@
         <v>500</v>
       </c>
       <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
         <v>800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>400</v>
       </c>
       <c r="G59" s="3">
         <v>400</v>
       </c>
       <c r="H59" s="3">
+        <v>400</v>
+      </c>
+      <c r="I59" s="3">
         <v>100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>600</v>
       </c>
       <c r="J59" s="3">
         <v>600</v>
       </c>
       <c r="K59" s="3">
+        <v>600</v>
+      </c>
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2886,38 +3023,41 @@
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E60" s="3">
         <v>18800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2933,38 +3073,41 @@
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E61" s="3">
         <v>56400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>56300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>56900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>83700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>54700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>36400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2980,32 +3123,35 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E62" s="3">
         <v>1400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3027,8 +3173,11 @@
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,38 +3323,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E66" s="3">
         <v>76700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>79700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>76600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>75700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>79300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>113900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>63100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>43800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3215,8 +3373,11 @@
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3349,19 +3517,19 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>287300</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>300800</v>
-      </c>
-      <c r="K70" s="3">
-        <v>287300</v>
       </c>
       <c r="L70" s="3">
         <v>287300</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>287300</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
@@ -3375,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,38 +3593,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-466900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-439000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-415300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-390300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-367200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-349900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-346600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-327400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-311700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3469,8 +3643,11 @@
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,41 +3793,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="E76" s="3">
         <v>6400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>28400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>50300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>70800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>84200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-325100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-307200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-292500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-252300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3657,8 +3843,11 @@
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,107 +3893,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-30200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,28 +4020,29 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I83" s="3">
-        <v>100</v>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -3864,13 +4063,16 @@
         <v>100</v>
       </c>
       <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,55 +4318,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-25100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-18000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-18700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
         <v>-12500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,55 +4390,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
       </c>
       <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
+      <c r="K91" s="3">
+        <v>-100</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,55 +4538,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-200</v>
       </c>
       <c r="F94" s="3">
         <v>-200</v>
       </c>
       <c r="G94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-100</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
+      <c r="K94" s="3">
+        <v>-100</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4610,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4409,8 +4643,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4424,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,40 +4808,43 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>101000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>28000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -4607,13 +4853,16 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>13400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>86500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4644,8 +4893,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4659,51 +4908,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-25400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-19000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>88200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16800</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-12500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>72200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GUTS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
   <si>
     <t>GUTS</t>
   </si>
@@ -656,90 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,11 +759,11 @@
       <c r="F8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -771,28 +778,34 @@
         <v>0</v>
       </c>
       <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
+      <c r="R8" s="3">
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -805,11 +818,11 @@
       <c r="F9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
+      <c r="G9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -829,11 +842,11 @@
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
@@ -844,8 +857,14 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,11 +877,11 @@
       <c r="F10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
@@ -882,11 +901,11 @@
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
@@ -897,8 +916,14 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,61 +943,69 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F12" s="3">
         <v>17500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>21200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>19400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>20300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>19000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>16800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>14400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>10200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>9400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>9100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>9300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>8600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>8500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>7800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>6400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,61 +1057,73 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>900</v>
+      </c>
+      <c r="F14" s="3">
         <v>1900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>2600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-6700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>18400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1092,34 +1137,34 @@
         <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1130,8 +1175,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,114 +1199,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F17" s="3">
         <v>22700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>26100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>24800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>25200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>23800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>23000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>21600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>13000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>13900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>11900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>12100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>11400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>11600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>12000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-22700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-26100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-24800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-25200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-23800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-23000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-21500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-13000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-13900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-11900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-12100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,119 +1340,133 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>20200</v>
+      </c>
+      <c r="F20" s="3">
         <v>21200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-4700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-10400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>5600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-43600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-26200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-23700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-24500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-21300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-18100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-11100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-18600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-14800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-11900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-12000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>-600</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>4</v>
@@ -1419,11 +1498,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1434,61 +1513,73 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-45600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-27900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-23700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-25000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-23200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-17200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-19200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-15700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-30200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-11900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-10900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-12500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-9100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1525,11 +1616,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1540,8 +1631,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1690,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-45600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-27900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-23700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-25000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-23200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-17200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-19200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-15700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-30200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-11900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-10900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-12500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-9100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-45600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-27900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-23700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-25000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-23200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-17200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-23500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-20100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-34500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-16200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-15200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-16900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-13400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1867,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1926,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1985,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,114 +2044,132 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-21200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>4700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>10400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-5600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-45600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-27900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-23700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-25000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-23200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-17200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-19200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-15700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-30200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-11900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-15200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-16900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-13400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2221,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-45600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-27900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-23700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-25000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-23200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-17200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-19200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-15700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-30200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-11900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-15200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-16900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-13400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2371,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,47 +2394,49 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>63200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>81500</v>
+      </c>
+      <c r="F41" s="3">
         <v>77700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>22300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>42100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>67500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>84700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>102400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>121400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>33200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>44500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>27700</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2276,8 +2449,14 @@
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,8 +2508,14 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2349,11 +2534,11 @@
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2362,14 +2547,14 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2382,8 +2567,14 @@
       <c r="S43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2396,11 +2587,11 @@
       <c r="F44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G44" s="3">
-        <v>100</v>
-      </c>
-      <c r="H44" s="3">
-        <v>100</v>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I44" s="3">
         <v>100</v>
@@ -2417,11 +2608,11 @@
       <c r="M44" s="3">
         <v>100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
+      <c r="N44" s="3">
+        <v>100</v>
+      </c>
+      <c r="O44" s="3">
+        <v>100</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
@@ -2435,8 +2626,14 @@
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2488,47 +2685,53 @@
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>87600</v>
+      </c>
+      <c r="F46" s="3">
         <v>79700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>26700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>47000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>71800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>87700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>106600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>124500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>35600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>46800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>29400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2541,8 +2744,14 @@
       <c r="S46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2579,11 +2788,11 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2594,47 +2803,53 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>29200</v>
+      </c>
+      <c r="F48" s="3">
         <v>29900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>30600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>31200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>31400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>31800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>32300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>31500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>30800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
@@ -2647,8 +2862,14 @@
       <c r="S48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2700,8 +2921,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2980,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,47 +3039,53 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F52" s="3">
         <v>4300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>4300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>4800</v>
       </c>
       <c r="G52" s="3">
         <v>4300</v>
       </c>
       <c r="H52" s="3">
-        <v>7500</v>
+        <v>4800</v>
       </c>
       <c r="I52" s="3">
-        <v>7600</v>
+        <v>4900</v>
       </c>
       <c r="J52" s="3">
         <v>7500</v>
       </c>
       <c r="K52" s="3">
+        <v>7600</v>
+      </c>
+      <c r="L52" s="3">
+        <v>7500</v>
+      </c>
+      <c r="M52" s="3">
         <v>6800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>6800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>7100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
@@ -2859,8 +3098,14 @@
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,47 +3157,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>121400</v>
+      </c>
+      <c r="F54" s="3">
         <v>114300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>62000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>83000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>108100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>126900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>146400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>163500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>76200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>56800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>38600</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2965,8 +3216,14 @@
       <c r="S54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3243,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,47 +3266,49 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3060,8 +3321,14 @@
       <c r="S57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3069,38 +3336,38 @@
         <v>5100</v>
       </c>
       <c r="E58" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="F58" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G58" s="3">
         <v>5000</v>
       </c>
       <c r="H58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J58" s="3">
         <v>4900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1100</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -3113,47 +3380,53 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>500</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E59" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F59" s="3">
         <v>500</v>
       </c>
       <c r="G59" s="3">
+        <v>500</v>
+      </c>
+      <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
@@ -3166,47 +3439,53 @@
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F60" s="3">
         <v>18700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>21800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>18800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>19800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>15700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>14300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>13300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>11200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3219,47 +3498,53 @@
       <c r="S60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>56500</v>
+      </c>
+      <c r="F61" s="3">
         <v>57100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>56700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>56400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>57500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>58000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>56300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>56900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>83700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>54700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>36400</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3272,41 +3557,47 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>37100</v>
+      </c>
+      <c r="F62" s="3">
         <v>41700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>9100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>19100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3325,8 +3616,14 @@
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3675,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3734,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,47 +3793,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>111900</v>
+      </c>
+      <c r="F66" s="3">
         <v>117500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>80200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>76700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>79700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>76600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>75700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>79300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>113900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>63100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>43800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3537,8 +3852,14 @@
       <c r="S66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3879,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3934,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3993,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3691,22 +4026,22 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
-        <v>287300</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>300800</v>
+        <v>0</v>
       </c>
       <c r="M70" s="3">
         <v>287300</v>
       </c>
       <c r="N70" s="3">
+        <v>300800</v>
+      </c>
+      <c r="O70" s="3">
         <v>287300</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>287300</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -3717,8 +4052,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,47 +4111,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-547000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-556300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-512500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-466900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-439000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-415300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-390300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-367200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-349900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-346600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-327400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-311700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3823,8 +4170,14 @@
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4229,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4288,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,50 +4347,56 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F76" s="3">
         <v>-3200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-18200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>28400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>50300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>70800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>84200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-325100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-307200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-292500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-252300</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4035,8 +4406,14 @@
       <c r="S76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4465,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-43700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-45600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-27900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-23700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-25000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-23200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-17200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-19200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-15700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-30200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-11900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-15200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-16900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-13400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-22900</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,37 +4615,39 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>100</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
@@ -4268,13 +4665,19 @@
         <v>100</v>
       </c>
       <c r="R83" s="3">
+        <v>100</v>
+      </c>
+      <c r="S83" s="3">
+        <v>100</v>
+      </c>
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4729,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4788,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4847,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4906,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4965,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-22700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-21200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-25100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-17000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-18000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-18700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-11700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-10600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-11000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-12500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-9900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-9300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,61 +5051,69 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +5165,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,61 +5224,73 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5310,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4883,11 +5350,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4898,8 +5365,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5424,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5483,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,61 +5542,73 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F100" s="3">
         <v>78100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1500</v>
-      </c>
-      <c r="F100" s="3">
-        <v>200</v>
-      </c>
-      <c r="G100" s="3">
-        <v>100</v>
       </c>
       <c r="H100" s="3">
         <v>200</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J100" s="3">
+        <v>200</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>101000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>28000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>13400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>86500</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5148,11 +5645,11 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5163,57 +5660,69 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F102" s="3">
         <v>55400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-19800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-25400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-17200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-18100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-19000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>88200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-11300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>16800</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-12500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-9900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>4100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>72200</v>
       </c>
     </row>
